--- a/DataTables/Datas/#Chapter.xlsx
+++ b/DataTables/Datas/#Chapter.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -45,6 +45,9 @@
     <t>waveGroups</t>
   </si>
   <si>
+    <t>AIParam</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
   </si>
   <si>
     <t>章节组</t>
+  </si>
+  <si>
+    <t>ai参数</t>
   </si>
   <si>
     <t>1001|1002|1003|1004|1005|1006|1007|1008|1009|1010</t>
@@ -1036,14 +1042,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="21.5" customWidth="1"/>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="54.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1059,53 +1065,65 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:5">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:5">
+    <row r="3" s="1" customFormat="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:5">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -1116,7 +1134,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -1127,7 +1145,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/#Chapter.xlsx
+++ b/DataTables/Datas/#Chapter.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -45,9 +45,6 @@
     <t>waveGroups</t>
   </si>
   <si>
-    <t>AIParam</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
   </si>
   <si>
     <t>章节组</t>
-  </si>
-  <si>
-    <t>ai参数</t>
   </si>
   <si>
     <t>1001|1002|1003|1004|1005|1006|1007|1008|1009|1010</t>
@@ -1065,68 +1059,60 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="F1"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="F2"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:6">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F3"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4"/>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:6">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1134,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="1:6">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1145,7 +1131,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
